--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="85">
   <si>
     <r>
       <rPr>
@@ -666,6 +666,9 @@
       </rPr>
       <t>CHI WEI RU</t>
     </r>
+  </si>
+  <si>
+    <t>张三</t>
   </si>
   <si>
     <r>
@@ -1352,11 +1355,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="4"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="6"/>
       <name val="SimSun"/>
@@ -1369,6 +1367,11 @@
     </font>
     <font>
       <sz val="5"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="4"/>
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
@@ -3748,7 +3751,7 @@
         <v>35</v>
       </c>
       <c r="AH11" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI11" s="7"/>
     </row>
@@ -3757,7 +3760,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>13</v>
@@ -3838,22 +3841,22 @@
         <v>33</v>
       </c>
       <c r="AC12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH12" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="AD12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH12" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="AI12" s="7"/>
     </row>
@@ -3862,7 +3865,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>45</v>
@@ -3922,43 +3925,43 @@
         <v>35</v>
       </c>
       <c r="V13" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="X13" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD13" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH13" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="W13" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="X13" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD13" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH13" s="12" t="s">
-        <v>49</v>
       </c>
       <c r="AI13" s="7"/>
     </row>
@@ -3967,7 +3970,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>45</v>
@@ -4006,7 +4009,7 @@
         <v>14</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P14" s="30" t="s">
         <v>34</v>
@@ -4018,16 +4021,16 @@
         <v>13</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W14" s="13" t="s">
         <v>13</v>
@@ -4063,7 +4066,7 @@
         <v>13</v>
       </c>
       <c r="AH14" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AI14" s="22">
         <v>2</v>
@@ -4074,7 +4077,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>13</v>
@@ -4170,7 +4173,7 @@
         <v>14</v>
       </c>
       <c r="AH15" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI15" s="22">
         <v>5</v>
@@ -4181,7 +4184,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>29</v>
@@ -4277,7 +4280,7 @@
         <v>36</v>
       </c>
       <c r="AH16" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI16" s="32">
         <v>5.5</v>
@@ -4288,7 +4291,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>35</v>
@@ -4384,7 +4387,7 @@
         <v>14</v>
       </c>
       <c r="AH17" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AI17" s="22">
         <v>1</v>
@@ -4395,7 +4398,7 @@
         <v>40</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>33</v>
@@ -4491,7 +4494,7 @@
         <v>33</v>
       </c>
       <c r="AH18" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AI18" s="22">
         <v>1</v>
@@ -4502,7 +4505,7 @@
         <v>43</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>35</v>
@@ -4571,34 +4574,34 @@
         <v>35</v>
       </c>
       <c r="Y19" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z19" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB19" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE19" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH19" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="AA19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB19" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE19" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH19" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="AI19" s="7"/>
     </row>
@@ -4607,7 +4610,7 @@
         <v>43</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>45</v>
@@ -4703,7 +4706,7 @@
         <v>13</v>
       </c>
       <c r="AH20" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AI20" s="7"/>
     </row>
@@ -4712,7 +4715,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>13</v>
@@ -4808,7 +4811,7 @@
         <v>35</v>
       </c>
       <c r="AH21" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI21" s="7"/>
     </row>
@@ -4817,7 +4820,7 @@
         <v>31</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>35</v>
@@ -4913,7 +4916,7 @@
         <v>14</v>
       </c>
       <c r="AH22" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI22" s="22">
         <v>3</v>
@@ -4924,7 +4927,7 @@
         <v>31</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="30" t="s">
         <v>36</v>
@@ -5020,7 +5023,7 @@
         <v>29</v>
       </c>
       <c r="AH23" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AI23" s="22">
         <v>9</v>
@@ -5031,7 +5034,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>13</v>
@@ -5127,7 +5130,7 @@
         <v>33</v>
       </c>
       <c r="AH24" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI24" s="32">
         <v>0.5</v>
@@ -5138,7 +5141,7 @@
         <v>40</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>38</v>
@@ -5234,7 +5237,7 @@
         <v>15</v>
       </c>
       <c r="AH25" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AI25" s="32">
         <v>8.5</v>
@@ -5245,7 +5248,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>15</v>
@@ -5254,10 +5257,10 @@
         <v>15</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>14</v>
@@ -5341,7 +5344,7 @@
         <v>35</v>
       </c>
       <c r="AH26" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI26" s="22">
         <v>0</v>
@@ -5352,7 +5355,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="30" t="s">
         <v>36</v>
@@ -5394,10 +5397,10 @@
         <v>35</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R27" s="12" t="s">
         <v>35</v>
@@ -5448,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="AH27" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI27" s="7"/>
     </row>
@@ -5457,7 +5460,7 @@
         <v>43</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>45</v>
@@ -5517,43 +5520,43 @@
         <v>13</v>
       </c>
       <c r="V28" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="W28" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z28" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD28" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE28" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF28" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH28" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="W28" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="X28" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y28" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z28" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD28" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE28" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF28" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH28" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="AI28" s="22">
         <v>-1</v>
@@ -5564,7 +5567,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>33</v>
@@ -5633,16 +5636,16 @@
         <v>13</v>
       </c>
       <c r="Y29" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z29" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA29" s="12" t="s">
         <v>13</v>
       </c>
       <c r="AB29" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC29" s="12" t="s">
         <v>35</v>
@@ -5660,28 +5663,28 @@
         <v>33</v>
       </c>
       <c r="AH29" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI29" s="7"/>
     </row>
     <row r="30" ht="13.25" customHeight="1" spans="1:35">
       <c r="A30" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G30" s="35" t="s">
         <v>35</v>
@@ -5696,7 +5699,7 @@
         <v>18</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L30" s="35" t="s">
         <v>35</v>
@@ -5705,44 +5708,44 @@
         <v>35</v>
       </c>
       <c r="N30" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="R30" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="S30" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="T30" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="U30" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="O30" s="17" t="s">
+      <c r="V30" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="P30" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q30" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="R30" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="S30" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="T30" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="U30" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="V30" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="W30" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X30" s="15" t="s">
         <v>18</v>
       </c>
       <c r="Y30" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z30" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="Z30" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="AA30" s="35" t="s">
         <v>35</v>
       </c>
@@ -5750,22 +5753,22 @@
         <v>35</v>
       </c>
       <c r="AC30" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD30" s="15" t="s">
         <v>18</v>
       </c>
       <c r="AE30" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG30" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH30" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI30" s="7"/>
     </row>
@@ -5820,7 +5823,7 @@
       <c r="AF31" s="25"/>
       <c r="AG31" s="25"/>
       <c r="AH31" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" s="22">
         <v>4</v>
@@ -5828,10 +5831,10 @@
     </row>
     <row r="32" ht="13.3" customHeight="1" spans="1:35">
       <c r="A32" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>30</v>
@@ -5931,7 +5934,7 @@
     </row>
     <row r="33" ht="13.55" customHeight="1" spans="1:35">
       <c r="A33" s="37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="38"/>
       <c r="C33" s="38"/>
@@ -5970,7 +5973,7 @@
     </row>
     <row r="34" ht="22.8" customHeight="1" spans="1:35">
       <c r="A34" s="37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="38"/>
       <c r="C34" s="38"/>
@@ -6009,7 +6012,7 @@
     </row>
     <row r="35" ht="41.5" customHeight="1" spans="1:35">
       <c r="A35" s="37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" s="38"/>
       <c r="C35" s="38"/>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="28800" windowHeight="14340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="73">
   <si>
     <r>
       <rPr>
@@ -51,6 +51,105 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欠休</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期五</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>六</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期一</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期二</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期三</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="4"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>星期四</t>
+    </r>
+  </si>
+  <si>
     <t>本月欠休</t>
   </si>
   <si>
@@ -61,10 +160,9 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>星期</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">本月休
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -72,73 +170,7 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>星期五</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>六</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>星期一</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>星期二</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>星期三</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>星期四</t>
+      <t>7天</t>
     </r>
   </si>
   <si>
@@ -720,7 +752,7 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>* AICU 行政值班：周青山主任 (13995521001)、金珺(18307556159) 、李旭（13688815565）                                                                                    7 May 2026 Version                                  2026年05月AICU值班表</t>
+      <t>* AICU 行政值班：周青山主任(13995521001)、金珺(18307556159) 、李旭（13688815565）                                                                                    7 May 2026 Version                                  2026年05月AICU值班表</t>
     </r>
   </si>
   <si>
@@ -821,7 +853,7 @@
     <numFmt numFmtId="178" formatCode="\ \ @"/>
     <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -833,19 +865,6 @@
       <sz val="4"/>
       <color rgb="FF000000"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="4"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="4"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1029,7 +1048,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="5"/>
+      <b/>
+      <sz val="4"/>
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
@@ -1047,6 +1067,11 @@
     <font>
       <sz val="5"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <name val="SimSun"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1268,7 +1293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1295,15 +1320,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1436,19 +1452,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1457,127 +1482,118 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1597,11 +1613,11 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1609,55 +1625,55 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1980,22 +1996,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AI38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="1" width="3.75833333333333" customWidth="1"/>
-    <col min="2" max="2" width="4.61666666666667" customWidth="1"/>
-    <col min="3" max="3" width="3.71666666666667" customWidth="1"/>
-    <col min="4" max="4" width="3.89166666666667" customWidth="1"/>
-    <col min="5" max="5" width="3.71666666666667" customWidth="1"/>
-    <col min="6" max="6" width="3.89166666666667" customWidth="1"/>
-    <col min="7" max="9" width="3.71666666666667" customWidth="1"/>
-    <col min="10" max="10" width="3.89166666666667" customWidth="1"/>
-    <col min="11" max="12" width="3.71666666666667" customWidth="1"/>
-    <col min="13" max="13" width="3.89166666666667" customWidth="1"/>
-    <col min="14" max="32" width="3.71666666666667" customWidth="1"/>
-    <col min="33" max="33" width="4.55833333333333" customWidth="1"/>
-    <col min="34" max="34" width="4.44166666666667" customWidth="1"/>
-    <col min="35" max="35" width="3.74166666666667" customWidth="1"/>
+    <col min="1" max="1" width="3.75806451612903" customWidth="1"/>
+    <col min="2" max="2" width="4.62096774193548" customWidth="1"/>
+    <col min="3" max="3" width="3.71774193548387" customWidth="1"/>
+    <col min="4" max="4" width="3.88709677419355" customWidth="1"/>
+    <col min="5" max="5" width="3.71774193548387" customWidth="1"/>
+    <col min="6" max="6" width="3.88709677419355" customWidth="1"/>
+    <col min="7" max="9" width="3.71774193548387" customWidth="1"/>
+    <col min="10" max="10" width="3.88709677419355" customWidth="1"/>
+    <col min="11" max="12" width="3.71774193548387" customWidth="1"/>
+    <col min="13" max="13" width="3.88709677419355" customWidth="1"/>
+    <col min="14" max="32" width="3.71774193548387" customWidth="1"/>
+    <col min="33" max="33" width="4.55645161290323" customWidth="1"/>
+    <col min="34" max="34" width="4.43548387096774" customWidth="1"/>
+    <col min="35" max="35" width="3.74193548387097" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.75" customHeight="1" spans="1:35">
@@ -2201,216 +2217,220 @@
       <c r="AG2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="10"/>
+      <c r="AH2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" ht="13.55" customHeight="1" spans="1:35">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="12" t="s">
         <v>14</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="X3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH3" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="AI3" s="7"/>
     </row>
     <row r="4" ht="13.3" customHeight="1" spans="1:35">
       <c r="A4" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG4" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI4" s="14">
         <v>1</v>
@@ -2418,106 +2438,106 @@
     </row>
     <row r="5" ht="13.55" customHeight="1" spans="1:35">
       <c r="A5" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH5" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="U5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD5" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH5" s="12" t="s">
-        <v>16</v>
       </c>
       <c r="AI5" s="14">
         <v>-1</v>
@@ -2525,106 +2545,106 @@
     </row>
     <row r="6" ht="13.45" customHeight="1" spans="1:35">
       <c r="A6" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="T6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH6" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="U6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG6" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH6" s="12" t="s">
-        <v>23</v>
       </c>
       <c r="AI6" s="14">
         <v>2</v>
@@ -2632,106 +2652,106 @@
     </row>
     <row r="7" ht="13.45" customHeight="1" spans="1:35">
       <c r="A7" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="V7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>19</v>
-      </c>
       <c r="W7" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y7" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA7" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC7" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD7" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE7" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF7" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG7" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH7" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI7" s="14">
         <v>2</v>
@@ -2739,106 +2759,106 @@
     </row>
     <row r="8" ht="13.45" customHeight="1" spans="1:35">
       <c r="A8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="AA8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="W8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE8" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="AF8" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG8" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH8" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AI8" s="20">
         <v>3.5</v>
@@ -2846,736 +2866,736 @@
     </row>
     <row r="9" ht="13.45" customHeight="1" spans="1:35">
       <c r="A9" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z9" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA9" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC9" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD9" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE9" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG9" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH9" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI9" s="7"/>
     </row>
     <row r="10" ht="13.45" customHeight="1" spans="1:35">
       <c r="A10" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="T10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="X10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH10" s="12" t="s">
         <v>34</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="T10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH10" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="AI10" s="7"/>
     </row>
     <row r="11" ht="13.45" customHeight="1" spans="1:35">
       <c r="A11" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="X11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH11" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="V11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="X11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH11" s="12" t="s">
-        <v>35</v>
       </c>
       <c r="AI11" s="7"/>
     </row>
     <row r="12" ht="13.45" customHeight="1" spans="1:35">
       <c r="A12" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z12" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA12" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC12" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE12" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH12" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI12" s="7"/>
     </row>
     <row r="13" ht="13.45" customHeight="1" spans="1:35">
       <c r="A13" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V13" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC13" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD13" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE13" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF13" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG13" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH13" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI13" s="7"/>
     </row>
     <row r="14" ht="13.3" customHeight="1" spans="1:35">
       <c r="A14" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA14" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB14" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC14" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD14" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE14" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF14" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH14" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI14" s="7"/>
     </row>
     <row r="15" ht="13.55" customHeight="1" spans="1:35">
       <c r="A15" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>41</v>
-      </c>
       <c r="I15" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="S15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="P15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="S15" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="T15" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U15" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Y15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA15" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC15" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="AD15" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE15" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF15" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG15" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH15" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AI15" s="14">
         <v>-2</v>
@@ -3583,106 +3603,106 @@
     </row>
     <row r="16" ht="13.45" customHeight="1" spans="1:35">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="R16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="S16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W16" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="X16" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y16" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z16" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA16" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AC16" s="17" t="s">
-        <v>19</v>
-      </c>
       <c r="AD16" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE16" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF16" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG16" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AI16" s="14">
         <v>3</v>
@@ -3690,106 +3710,106 @@
     </row>
     <row r="17" ht="13.45" customHeight="1" spans="1:35">
       <c r="A17" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="Q17" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V17" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X17" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y17" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z17" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA17" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB17" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC17" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD17" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF17" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AF17" s="16" t="s">
-        <v>19</v>
-      </c>
       <c r="AG17" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH17" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI17" s="20">
         <v>3.5</v>
@@ -3797,106 +3817,106 @@
     </row>
     <row r="18" ht="13.45" customHeight="1" spans="1:35">
       <c r="A18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>26</v>
-      </c>
       <c r="M18" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R18" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA18" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB18" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD18" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE18" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF18" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG18" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH18" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AI18" s="14">
         <v>-1</v>
@@ -3904,106 +3924,106 @@
     </row>
     <row r="19" ht="13.45" customHeight="1" spans="1:35">
       <c r="A19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="X19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z19" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="S19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="X19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z19" s="19" t="s">
-        <v>26</v>
-      </c>
       <c r="AA19" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB19" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC19" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD19" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE19" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG19" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH19" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI19" s="14">
         <v>1</v>
@@ -4011,631 +4031,631 @@
     </row>
     <row r="20" ht="13.45" customHeight="1" spans="1:35">
       <c r="A20" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="X20" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z20" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA20" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB20" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC20" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD20" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE20" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF20" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG20" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH20" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI20" s="7"/>
     </row>
     <row r="21" ht="13.45" customHeight="1" spans="1:35">
       <c r="A21" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="K21" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R21" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y21" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB21" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC21" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD21" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE21" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF21" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG21" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH21" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AI21" s="7"/>
     </row>
     <row r="22" ht="13.45" customHeight="1" spans="1:35">
       <c r="A22" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W22" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z22" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA22" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB22" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC22" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE22" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF22" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH22" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AI22" s="7"/>
     </row>
     <row r="23" ht="13.45" customHeight="1" spans="1:35">
       <c r="A23" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA23" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB23" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE23" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH23" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AI23" s="7"/>
     </row>
     <row r="24" ht="13.3" customHeight="1" spans="1:35">
       <c r="A24" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="N24" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z24" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA24" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB24" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD24" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE24" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF24" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG24" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH24" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AI24" s="7"/>
     </row>
     <row r="25" ht="13.55" customHeight="1" spans="1:35">
       <c r="A25" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="L25" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R25" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S25" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="X25" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y25" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="T25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="X25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y25" s="13" t="s">
+      <c r="AB25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Z25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD25" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="AE25" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF25" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG25" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH25" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AI25" s="14">
         <v>2</v>
@@ -4643,106 +4663,106 @@
     </row>
     <row r="26" ht="13.45" customHeight="1" spans="1:35">
       <c r="A26" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T26" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="U26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="X26" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y26" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="O26" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P26" s="12" t="s">
+      <c r="Z26" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA26" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG26" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="Q26" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="V26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="X26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y26" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA26" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB26" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC26" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD26" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG26" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="AH26" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AI26" s="14">
         <v>9</v>
@@ -4750,106 +4770,106 @@
     </row>
     <row r="27" ht="13.45" customHeight="1" spans="1:35">
       <c r="A27" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="S27" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="T27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y27" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z27" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R27" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="S27" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="T27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z27" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="AA27" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AB27" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD27" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE27" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF27" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG27" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH27" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AI27" s="20">
         <v>1.5</v>
@@ -4857,106 +4877,106 @@
     </row>
     <row r="28" ht="13.45" customHeight="1" spans="1:35">
       <c r="A28" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S28" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S28" s="19" t="s">
-        <v>26</v>
-      </c>
       <c r="T28" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V28" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z28" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA28" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB28" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE28" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF28" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG28" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH28" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AI28" s="20">
         <v>4.5</v>
@@ -4964,631 +4984,631 @@
     </row>
     <row r="29" ht="13.45" customHeight="1" spans="1:35">
       <c r="A29" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S29" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y29" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z29" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB29" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE29" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF29" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG29" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH29" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AI29" s="7"/>
     </row>
     <row r="30" ht="13.45" customHeight="1" spans="1:35">
       <c r="A30" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X30" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y30" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z30" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE30" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF30" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG30" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH30" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AI30" s="7"/>
     </row>
     <row r="31" ht="13.45" customHeight="1" spans="1:35">
       <c r="A31" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O31" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S31" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z31" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA31" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB31" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE31" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF31" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG31" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH31" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AI31" s="7"/>
     </row>
     <row r="32" ht="13.45" customHeight="1" spans="1:35">
       <c r="A32" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S32" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U32" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y32" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z32" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC32" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD32" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE32" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF32" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG32" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH32" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AI32" s="7"/>
     </row>
     <row r="33" ht="13.45" customHeight="1" spans="1:35">
       <c r="A33" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S33" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V33" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y33" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z33" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA33" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB33" s="17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD33" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE33" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF33" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG33" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH33" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AI33" s="7"/>
     </row>
     <row r="34" ht="13.45" customHeight="1" spans="1:35">
       <c r="A34" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE34" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG34" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH34" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AI34" s="14">
         <v>4</v>
@@ -5596,110 +5616,110 @@
     </row>
     <row r="35" ht="13.3" customHeight="1" spans="1:35">
       <c r="A35" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S35" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y35" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z35" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE35" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF35" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG35" s="13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH35" s="7"/>
       <c r="AI35" s="7"/>
     </row>
     <row r="36" ht="13.55" customHeight="1" spans="1:35">
       <c r="A36" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -5738,7 +5758,7 @@
     </row>
     <row r="37" ht="22.8" customHeight="1" spans="1:35">
       <c r="A37" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
@@ -5777,7 +5797,7 @@
     </row>
     <row r="38" ht="46.5" customHeight="1" spans="1:35">
       <c r="A38" s="25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
@@ -5816,10 +5836,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="A36:AI36"/>
     <mergeCell ref="A37:AI37"/>
     <mergeCell ref="A38:AI38"/>
-    <mergeCell ref="AH1:AI2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -155,27 +155,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">本月休
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7天</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="4"/>
         <rFont val="SimSun"/>
         <charset val="134"/>
@@ -442,7 +421,7 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>脱产</t>
+      <t>迎新</t>
     </r>
   </si>
   <si>
@@ -482,16 +461,6 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>迎新</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
       <t>宁雨露</t>
     </r>
   </si>
@@ -692,16 +661,6 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>事假</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
       <t>林珊珊</t>
     </r>
   </si>
@@ -712,16 +671,6 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>事假/值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
       <t>行政</t>
     </r>
   </si>
@@ -752,7 +701,7 @@
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>* AICU 行政值班：周青山主任(13995521001)、金珺(18307556159) 、李旭（13688815565）                                                                                    7 May 2026 Version                                  2026年05月AICU值班表</t>
+      <t>* AICU 行政值班：周青山主任(13995521001)、金珺(18307556159) 、李旭（13688815565）                                                                                    30 Apr 2026 Version                                 2026年05月AICU值班表</t>
     </r>
   </si>
   <si>
@@ -864,6 +813,12 @@
       <b/>
       <sz val="4"/>
       <color rgb="FF000000"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="4"/>
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
@@ -1043,17 +998,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="4"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="4"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="6"/>
       <name val="SimSun"/>
@@ -1070,12 +1014,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="4"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="5"/>
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1091,12 +1040,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6B8B7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1452,152 +1395,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1628,52 +1571,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2004,11 +1941,7 @@
     <col min="4" max="4" width="3.88709677419355" customWidth="1"/>
     <col min="5" max="5" width="3.71774193548387" customWidth="1"/>
     <col min="6" max="6" width="3.88709677419355" customWidth="1"/>
-    <col min="7" max="9" width="3.71774193548387" customWidth="1"/>
-    <col min="10" max="10" width="3.88709677419355" customWidth="1"/>
-    <col min="11" max="12" width="3.71774193548387" customWidth="1"/>
-    <col min="13" max="13" width="3.88709677419355" customWidth="1"/>
-    <col min="14" max="32" width="3.71774193548387" customWidth="1"/>
+    <col min="7" max="32" width="3.71774193548387" customWidth="1"/>
     <col min="33" max="33" width="4.55645161290323" customWidth="1"/>
     <col min="34" max="34" width="4.43548387096774" customWidth="1"/>
     <col min="35" max="35" width="3.74193548387097" customWidth="1"/>
@@ -2221,216 +2154,216 @@
         <v>11</v>
       </c>
       <c r="AI2" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1" spans="1:35">
       <c r="A3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE3" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" ht="13.3" customHeight="1" spans="1:35">
+    <row r="4" ht="13.35" customHeight="1" spans="1:35">
       <c r="A4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH4" s="12" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="V4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="X4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH4" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="AI4" s="14">
         <v>1</v>
@@ -2438,106 +2371,106 @@
     </row>
     <row r="5" ht="13.55" customHeight="1" spans="1:35">
       <c r="A5" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="J5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="M5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="P5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="15" t="s">
+      <c r="T5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="U5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="W5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z5" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE5" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="AF5" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH5" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5" s="14">
         <v>-1</v>
@@ -2545,1164 +2478,1166 @@
     </row>
     <row r="6" ht="13.45" customHeight="1" spans="1:35">
       <c r="A6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>25</v>
-      </c>
       <c r="C6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="K6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S6" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="T6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="U6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y6" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="Z6" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC6" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD6" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE6" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG6" s="19" t="s">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="AG6" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="AH6" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="13.45" customHeight="1" spans="1:35">
       <c r="A7" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="H7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="U7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="V7" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y7" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Z7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC7" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH7" s="12" t="s">
-        <v>29</v>
-      </c>
       <c r="AI7" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="13.45" customHeight="1" spans="1:35">
       <c r="A8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="K8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="AA8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W8" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z8" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA8" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="AB8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC8" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD8" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE8" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF8" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG8" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI8" s="20">
+        <v>30</v>
+      </c>
+      <c r="AI8" s="19">
         <v>3.5</v>
       </c>
     </row>
     <row r="9" ht="13.45" customHeight="1" spans="1:35">
       <c r="A9" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC9" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD9" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE9" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG9" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI9" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="AI9" s="14">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10" ht="13.45" customHeight="1" spans="1:35">
       <c r="A10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="C10" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="G10" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V10" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC10" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD10" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF10" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG10" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH10" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AI10" s="7"/>
     </row>
     <row r="11" ht="13.45" customHeight="1" spans="1:35">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="I11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q11" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y11" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF11" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG11" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH11" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AI11" s="7"/>
     </row>
     <row r="12" ht="13.45" customHeight="1" spans="1:35">
       <c r="A12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="T12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="12" t="s">
-        <v>41</v>
-      </c>
       <c r="U12" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V12" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y12" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z12" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA12" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF12" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG12" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH12" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AI12" s="7"/>
     </row>
     <row r="13" ht="13.45" customHeight="1" spans="1:35">
       <c r="A13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V13" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC13" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE13" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF13" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH13" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI13" s="7"/>
     </row>
-    <row r="14" ht="13.3" customHeight="1" spans="1:35">
+    <row r="14" ht="13.35" customHeight="1" spans="1:35">
       <c r="A14" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB14" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC14" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD14" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE14" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF14" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH14" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI14" s="7"/>
     </row>
     <row r="15" ht="13.55" customHeight="1" spans="1:35">
       <c r="A15" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="O15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W15" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="S15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="T15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="V15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="W15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH15" s="12" t="s">
-        <v>45</v>
-      </c>
       <c r="AI15" s="14">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="16" ht="13.45" customHeight="1" spans="1:35">
       <c r="A16" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="F16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T16" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="S16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T16" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W16" s="15" t="s">
+      <c r="AC16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="X16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y16" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC16" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="AD16" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG16" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH16" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AI16" s="14">
         <v>3</v>
@@ -3710,213 +3645,213 @@
     </row>
     <row r="17" ht="13.45" customHeight="1" spans="1:35">
       <c r="A17" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="P17" s="15" t="s">
+      <c r="AF17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="Q17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="V17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z17" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE17" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF17" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="AG17" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH17" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI17" s="20">
-        <v>3.5</v>
+        <v>46</v>
+      </c>
+      <c r="AI17" s="19">
+        <v>2.5</v>
       </c>
     </row>
     <row r="18" ht="13.45" customHeight="1" spans="1:35">
       <c r="A18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="M18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="17" t="s">
+      <c r="O18" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="S18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="R18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="S18" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="T18" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="U18" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V18" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA18" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB18" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC18" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD18" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE18" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG18" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH18" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AI18" s="14">
         <v>-1</v>
@@ -3924,1691 +3859,1691 @@
     </row>
     <row r="19" ht="13.45" customHeight="1" spans="1:35">
       <c r="A19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="X19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z19" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="16" t="s">
+      <c r="AA19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG19" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="M19" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="X19" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z19" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD19" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE19" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG19" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="AH19" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI19" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="13.45" customHeight="1" spans="1:35">
       <c r="A20" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="I20" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>39</v>
+        <v>14</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V20" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X20" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z20" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD20" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE20" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF20" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH20" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI20" s="7"/>
     </row>
     <row r="21" ht="13.45" customHeight="1" spans="1:35">
       <c r="A21" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y21" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z21" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC21" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD21" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE21" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF21" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG21" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI21" s="7"/>
     </row>
     <row r="22" ht="13.45" customHeight="1" spans="1:35">
       <c r="A22" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q22" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W22" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z22" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA22" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB22" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC22" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE22" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF22" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH22" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AI22" s="7"/>
     </row>
     <row r="23" ht="13.45" customHeight="1" spans="1:35">
       <c r="A23" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I23" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA23" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB23" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE23" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG23" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH23" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AI23" s="7"/>
     </row>
-    <row r="24" ht="13.3" customHeight="1" spans="1:35">
+    <row r="24" ht="13.35" customHeight="1" spans="1:35">
       <c r="A24" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I24" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="18" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="X24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="X24" s="17" t="s">
         <v>26</v>
       </c>
       <c r="Y24" s="13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z24" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA24" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB24" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD24" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE24" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="AE24" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="AF24" s="13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG24" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI24" s="7"/>
     </row>
     <row r="25" ht="13.55" customHeight="1" spans="1:35">
       <c r="A25" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="G25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q25" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="R25" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="S25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V25" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W25" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K25" s="15" t="s">
+      <c r="X25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="N25" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="P25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q25" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="S25" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="X25" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="Y25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z25" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA25" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB25" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD25" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE25" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF25" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG25" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH25" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AI25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="13.45" customHeight="1" spans="1:35">
       <c r="A26" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="J26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O26" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="U26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="X26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB26" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="T26" s="12" t="s">
+      <c r="AD26" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG26" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="U26" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="V26" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="X26" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y26" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z26" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC26" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD26" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE26" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG26" s="15" t="s">
-        <v>20</v>
-      </c>
       <c r="AH26" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AI26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" ht="13.45" customHeight="1" spans="1:35">
       <c r="A27" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R27" s="19" t="s">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="S27" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U27" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V27" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y27" s="13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Z27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA27" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AA27" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="AB27" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD27" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE27" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF27" s="19" t="s">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="AF27" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="AG27" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH27" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI27" s="20">
-        <v>1.5</v>
+        <v>56</v>
+      </c>
+      <c r="AI27" s="19">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" ht="13.45" customHeight="1" spans="1:35">
       <c r="A28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="H28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="J28" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="S28" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P28" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="S28" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="T28" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V28" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y28" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z28" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA28" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB28" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE28" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF28" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG28" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH28" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI28" s="20">
-        <v>4.5</v>
+        <v>57</v>
+      </c>
+      <c r="AI28" s="19">
+        <v>3.5</v>
       </c>
     </row>
     <row r="29" ht="13.45" customHeight="1" spans="1:35">
       <c r="A29" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S29" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="U29" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X29" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="R29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="T29" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="W29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="X29" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="Y29" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA29" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB29" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE29" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH29" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AI29" s="7"/>
     </row>
     <row r="30" ht="13.45" customHeight="1" spans="1:35">
       <c r="A30" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X30" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z30" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA30" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE30" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF30" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG30" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH30" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AI30" s="7"/>
     </row>
     <row r="31" ht="13.45" customHeight="1" spans="1:35">
       <c r="A31" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I31" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O31" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S31" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y31" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z31" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA31" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB31" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF31" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG31" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH31" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AI31" s="7"/>
     </row>
     <row r="32" ht="13.45" customHeight="1" spans="1:35">
       <c r="A32" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I32" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S32" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U32" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V32" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y32" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z32" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC32" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD32" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE32" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF32" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG32" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH32" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AI32" s="7"/>
     </row>
     <row r="33" ht="13.45" customHeight="1" spans="1:35">
       <c r="A33" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I33" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S33" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V33" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y33" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z33" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA33" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB33" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD33" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE33" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF33" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG33" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH33" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AI33" s="7"/>
     </row>
     <row r="34" ht="13.45" customHeight="1" spans="1:35">
       <c r="A34" s="11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE34" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG34" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH34" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AI34" s="14">
         <v>4</v>
@@ -5616,223 +5551,223 @@
     </row>
     <row r="35" ht="13.3" customHeight="1" spans="1:35">
       <c r="A35" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="S35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="T35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="U35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="V35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="W35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="X35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="Y35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="Z35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="AA35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="AB35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="AC35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="N35" s="12" t="s">
+      <c r="AD35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="O35" s="12" t="s">
+      <c r="AE35" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="P35" s="12" t="s">
+      <c r="AF35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Q35" s="12" t="s">
+      <c r="AG35" s="13" t="s">
         <v>17</v>
-      </c>
-      <c r="R35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="S35" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="T35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="U35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="V35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="W35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y35" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z35" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE35" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF35" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG35" s="13" t="s">
-        <v>18</v>
       </c>
       <c r="AH35" s="7"/>
       <c r="AI35" s="7"/>
     </row>
     <row r="36" ht="13.55" customHeight="1" spans="1:35">
-      <c r="A36" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="24"/>
-      <c r="AE36" s="24"/>
-      <c r="AF36" s="24"/>
-      <c r="AG36" s="24"/>
-      <c r="AH36" s="24"/>
-      <c r="AI36" s="24"/>
+      <c r="A36" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="22"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="22"/>
+      <c r="AB36" s="22"/>
+      <c r="AC36" s="22"/>
+      <c r="AD36" s="22"/>
+      <c r="AE36" s="22"/>
+      <c r="AF36" s="22"/>
+      <c r="AG36" s="22"/>
+      <c r="AH36" s="22"/>
+      <c r="AI36" s="22"/>
     </row>
     <row r="37" ht="22.8" customHeight="1" spans="1:35">
-      <c r="A37" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="24"/>
-      <c r="U37" s="24"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="24"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="24"/>
-      <c r="AC37" s="24"/>
-      <c r="AD37" s="24"/>
-      <c r="AE37" s="24"/>
-      <c r="AF37" s="24"/>
-      <c r="AG37" s="24"/>
-      <c r="AH37" s="24"/>
-      <c r="AI37" s="24"/>
+      <c r="A37" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="22"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="22"/>
+      <c r="Z37" s="22"/>
+      <c r="AA37" s="22"/>
+      <c r="AB37" s="22"/>
+      <c r="AC37" s="22"/>
+      <c r="AD37" s="22"/>
+      <c r="AE37" s="22"/>
+      <c r="AF37" s="22"/>
+      <c r="AG37" s="22"/>
+      <c r="AH37" s="22"/>
+      <c r="AI37" s="22"/>
     </row>
     <row r="38" ht="46.5" customHeight="1" spans="1:35">
-      <c r="A38" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
-      <c r="AC38" s="24"/>
-      <c r="AD38" s="24"/>
-      <c r="AE38" s="24"/>
-      <c r="AF38" s="24"/>
-      <c r="AG38" s="24"/>
-      <c r="AH38" s="24"/>
-      <c r="AI38" s="24"/>
+      <c r="A38" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
+      <c r="W38" s="22"/>
+      <c r="X38" s="22"/>
+      <c r="Y38" s="22"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22"/>
+      <c r="AE38" s="22"/>
+      <c r="AF38" s="22"/>
+      <c r="AG38" s="22"/>
+      <c r="AH38" s="22"/>
+      <c r="AI38" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -231,6 +231,61 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
+      <t xml:space="preserve">学习</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">二线医生</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">龚少峰</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">夜</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">机1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
       <t xml:space="preserve">机</t>
     </r>
   </si>
@@ -240,52 +295,6 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
-      <t xml:space="preserve">二线医生</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">龚少峰</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">夜</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">机1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
       <t xml:space="preserve">吴丽丽</t>
     </r>
   </si>
@@ -421,6 +430,15 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
+      <t xml:space="preserve">事假/值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
       <t xml:space="preserve">宁雨露</t>
     </r>
   </si>
@@ -611,15 +629,6 @@
         <rFont val="宋体"/>
       </rPr>
       <t xml:space="preserve">林珊珊</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">事假/值</t>
     </r>
   </si>
   <si>
@@ -1866,14 +1875,14 @@
       <c r="AC5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AD5" s="16" t="s">
+      <c r="AD5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="AE5" s="16" t="s">
-        <v>19</v>
+      <c r="AE5" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG5" s="17" t="s">
         <v>13</v>
@@ -1883,7 +1892,7 @@
         <v>16</v>
       </c>
       <c r="AJ5" s="18">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="13.00" customHeight="1">
@@ -1974,24 +1983,24 @@
       <c r="AC6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>14</v>
+      <c r="AD6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="20" t="s">
+        <v>19</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG6" s="21" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AH6" s="6"/>
       <c r="AI6" s="16" t="s">
         <v>23</v>
       </c>
       <c r="AJ6" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="14.00" customHeight="1">
@@ -1999,7 +2008,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>13</v>
@@ -2041,7 +2050,7 @@
         <v>13</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q7" s="16" t="s">
         <v>14</v>
@@ -2056,7 +2065,7 @@
         <v>24</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="V7" s="16" t="s">
         <v>19</v>
@@ -2085,8 +2094,8 @@
       <c r="AD7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AE7" s="16" t="s">
-        <v>13</v>
+      <c r="AE7" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="AF7" s="21" t="s">
         <v>26</v>
@@ -2096,18 +2105,18 @@
       </c>
       <c r="AH7" s="6"/>
       <c r="AI7" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ7" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="13.00" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>24</v>
@@ -2131,7 +2140,7 @@
         <v>14</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>25</v>
@@ -2182,7 +2191,7 @@
         <v>26</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AB8" s="16" t="s">
         <v>19</v>
@@ -2196,26 +2205,26 @@
       <c r="AE8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AF8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG8" s="17" t="s">
-        <v>13</v>
+      <c r="AF8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG8" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="AH8" s="6"/>
       <c r="AI8" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ8" s="22">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="14.00" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>20</v>
@@ -2248,7 +2257,7 @@
         <v>24</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N9" s="16" t="s">
         <v>25</v>
@@ -2312,28 +2321,28 @@
       </c>
       <c r="AH9" s="6"/>
       <c r="AI9" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AJ9" s="13"/>
     </row>
     <row r="10" spans="1:36" ht="13.00" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>13</v>
@@ -2418,43 +2427,43 @@
       </c>
       <c r="AH10" s="6"/>
       <c r="AI10" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ10" s="13"/>
     </row>
     <row r="11" spans="1:36" ht="14.00" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L11" s="17" t="s">
         <v>13</v>
@@ -2466,13 +2475,13 @@
         <v>24</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R11" s="17" t="s">
         <v>13</v>
@@ -2524,29 +2533,29 @@
       </c>
       <c r="AH11" s="6"/>
       <c r="AI11" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AJ11" s="13"/>
     </row>
     <row r="12" spans="1:36" ht="13.00" customHeight="1">
       <c r="A12" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>33</v>
-      </c>
       <c r="G12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2562,8 +2571,8 @@
       <c r="K12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="17" t="s">
-        <v>24</v>
+      <c r="L12" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>25</v>
@@ -2571,8 +2580,8 @@
       <c r="N12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="O12" s="16" t="s">
-        <v>13</v>
+      <c r="O12" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="P12" s="16" t="s">
         <v>24</v>
@@ -2587,13 +2596,13 @@
         <v>24</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U12" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V12" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W12" s="16" t="s">
         <v>24</v>
@@ -2630,34 +2639,34 @@
       </c>
       <c r="AH12" s="6"/>
       <c r="AI12" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AJ12" s="13"/>
     </row>
     <row r="13" spans="1:36" ht="13.00" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>24</v>
@@ -2710,8 +2719,8 @@
       <c r="Y13" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Z13" s="17" t="s">
-        <v>24</v>
+      <c r="Z13" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="AA13" s="16" t="s">
         <v>24</v>
@@ -2736,35 +2745,35 @@
       </c>
       <c r="AH13" s="6"/>
       <c r="AI13" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AJ13" s="13"/>
     </row>
     <row r="14" spans="1:36" ht="14.00" customHeight="1">
       <c r="A14" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>41</v>
-      </c>
       <c r="I14" s="16" t="s">
         <v>24</v>
       </c>
@@ -2774,8 +2783,8 @@
       <c r="K14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="17" t="s">
-        <v>13</v>
+      <c r="L14" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>13</v>
@@ -2783,8 +2792,8 @@
       <c r="N14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="16" t="s">
-        <v>24</v>
+      <c r="O14" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="P14" s="16" t="s">
         <v>25</v>
@@ -2842,7 +2851,7 @@
       </c>
       <c r="AH14" s="6"/>
       <c r="AI14" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ14" s="13"/>
     </row>
@@ -2851,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>13</v>
@@ -2869,7 +2878,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>14</v>
@@ -2878,10 +2887,10 @@
         <v>18</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" s="19" t="s">
         <v>18</v>
@@ -2931,24 +2940,24 @@
       <c r="AB15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AC15" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD15" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE15" s="16" t="s">
+      <c r="AC15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE15" s="20" t="s">
         <v>13</v>
       </c>
       <c r="AF15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AG15" s="17" t="s">
-        <v>13</v>
+      <c r="AG15" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="AH15" s="6"/>
       <c r="AI15" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AJ15" s="18">
         <v>-2</v>
@@ -2959,7 +2968,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>24</v>
@@ -3037,16 +3046,16 @@
         <v>14</v>
       </c>
       <c r="AB16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD16" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE16" s="16" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="AC16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD16" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE16" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="AF16" s="17" t="s">
         <v>13</v>
@@ -3056,10 +3065,10 @@
       </c>
       <c r="AH16" s="6"/>
       <c r="AI16" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AJ16" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="13.00" customHeight="1">
@@ -3067,7 +3076,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>20</v>
@@ -3154,7 +3163,7 @@
         <v>14</v>
       </c>
       <c r="AE17" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AF17" s="17" t="s">
         <v>19</v>
@@ -3164,7 +3173,7 @@
       </c>
       <c r="AH17" s="6"/>
       <c r="AI17" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ17" s="22">
         <v>3.5</v>
@@ -3172,10 +3181,10 @@
     </row>
     <row r="18" spans="1:36" ht="14.00" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>25</v>
@@ -3193,7 +3202,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>25</v>
@@ -3204,14 +3213,14 @@
       <c r="K18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L18" s="21" t="s">
-        <v>26</v>
+      <c r="L18" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>25</v>
@@ -3229,7 +3238,7 @@
         <v>14</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="U18" s="16" t="s">
         <v>25</v>
@@ -3258,8 +3267,8 @@
       <c r="AC18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD18" s="16" t="s">
-        <v>13</v>
+      <c r="AD18" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="AE18" s="16" t="s">
         <v>14</v>
@@ -3272,18 +3281,18 @@
       </c>
       <c r="AH18" s="6"/>
       <c r="AI18" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AJ18" s="18">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="13.00" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>24</v>
@@ -3307,10 +3316,10 @@
         <v>13</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L19" s="17" t="s">
         <v>25</v>
@@ -3328,7 +3337,7 @@
         <v>24</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R19" s="17" t="s">
         <v>25</v>
@@ -3343,7 +3352,7 @@
         <v>14</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="W19" s="16" t="s">
         <v>24</v>
@@ -3366,71 +3375,69 @@
       <c r="AC19" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE19" s="16" t="s">
-        <v>20</v>
+      <c r="AD19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE19" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="AF19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AG19" s="21" t="s">
-        <v>26</v>
+      <c r="AG19" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AH19" s="6"/>
       <c r="AI19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ19" s="18">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="AJ19" s="13"/>
     </row>
     <row r="20" spans="1:36" ht="14.00" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L20" s="17" t="s">
         <v>13</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P20" s="16" t="s">
         <v>13</v>
@@ -3488,49 +3495,49 @@
       </c>
       <c r="AH20" s="6"/>
       <c r="AI20" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AJ20" s="13"/>
     </row>
     <row r="21" spans="1:36" ht="13.00" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="20" t="s">
-        <v>33</v>
       </c>
       <c r="N21" s="16" t="s">
         <v>13</v>
@@ -3594,34 +3601,34 @@
       </c>
       <c r="AH21" s="6"/>
       <c r="AI21" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AJ21" s="13"/>
     </row>
     <row r="22" spans="1:36" ht="13.00" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>24</v>
@@ -3700,34 +3707,34 @@
       </c>
       <c r="AH22" s="6"/>
       <c r="AI22" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AJ22" s="13"/>
     </row>
     <row r="23" spans="1:36" ht="14.00" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>25</v>
@@ -3806,40 +3813,40 @@
       </c>
       <c r="AH23" s="6"/>
       <c r="AI23" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AJ23" s="13"/>
     </row>
     <row r="24" spans="1:36" ht="13.00" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>24</v>
@@ -3848,7 +3855,7 @@
         <v>24</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N24" s="16" t="s">
         <v>24</v>
@@ -3912,7 +3919,7 @@
       </c>
       <c r="AH24" s="6"/>
       <c r="AI24" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AJ24" s="13"/>
     </row>
@@ -3921,7 +3928,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>13</v>
@@ -3984,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="W25" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="X25" s="16" t="s">
         <v>19</v>
@@ -4004,24 +4011,24 @@
       <c r="AC25" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AD25" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE25" s="16" t="s">
-        <v>14</v>
+      <c r="AD25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE25" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="AF25" s="17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AG25" s="17" t="s">
         <v>13</v>
       </c>
       <c r="AH25" s="6"/>
       <c r="AI25" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AJ25" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:36" ht="13.00" customHeight="1">
@@ -4029,7 +4036,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>24</v>
@@ -4041,7 +4048,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>13</v>
@@ -4058,8 +4065,8 @@
       <c r="K26" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L26" s="21" t="s">
-        <v>26</v>
+      <c r="L26" s="20" t="s">
+        <v>24</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>14</v>
@@ -4110,7 +4117,7 @@
         <v>13</v>
       </c>
       <c r="AC26" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AD26" s="16" t="s">
         <v>19</v>
@@ -4126,10 +4133,10 @@
       </c>
       <c r="AH26" s="6"/>
       <c r="AI26" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AJ26" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:36" ht="14.00" customHeight="1">
@@ -4137,7 +4144,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>19</v>
@@ -4220,8 +4227,8 @@
       <c r="AC27" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD27" s="16" t="s">
-        <v>14</v>
+      <c r="AD27" s="20" t="s">
+        <v>18</v>
       </c>
       <c r="AE27" s="16" t="s">
         <v>14</v>
@@ -4234,7 +4241,7 @@
       </c>
       <c r="AH27" s="6"/>
       <c r="AI27" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AJ27" s="22">
         <v>1.5</v>
@@ -4242,10 +4249,10 @@
     </row>
     <row r="28" spans="1:36" ht="13.00" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>24</v>
@@ -4266,7 +4273,7 @@
         <v>24</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J28" s="16" t="s">
         <v>25</v>
@@ -4284,7 +4291,7 @@
         <v>14</v>
       </c>
       <c r="O28" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P28" s="16" t="s">
         <v>25</v>
@@ -4328,8 +4335,8 @@
       <c r="AC28" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AD28" s="16" t="s">
-        <v>13</v>
+      <c r="AD28" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="AE28" s="16" t="s">
         <v>13</v>
@@ -4342,10 +4349,10 @@
       </c>
       <c r="AH28" s="6"/>
       <c r="AI28" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AJ28" s="22">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29" spans="1:36" ht="14.00" customHeight="1">
@@ -4353,7 +4360,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>13</v>
@@ -4365,7 +4372,7 @@
         <v>13</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>25</v>
@@ -4419,65 +4426,67 @@
         <v>14</v>
       </c>
       <c r="X29" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y29" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB29" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD29" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="Y29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z29" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA29" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB29" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC29" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD29" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE29" s="16" t="s">
-        <v>25</v>
+      <c r="AE29" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="AF29" s="17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG29" s="17" t="s">
         <v>13</v>
       </c>
       <c r="AH29" s="6"/>
       <c r="AI29" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ29" s="13"/>
+        <v>60</v>
+      </c>
+      <c r="AJ29" s="18">
+        <v>-1</v>
+      </c>
     </row>
     <row r="30" spans="1:36" ht="13.00" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>24</v>
@@ -4556,34 +4565,34 @@
       </c>
       <c r="AH30" s="6"/>
       <c r="AI30" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AJ30" s="13"/>
     </row>
     <row r="31" spans="1:36" ht="13.00" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>25</v>
@@ -4662,40 +4671,40 @@
       </c>
       <c r="AH31" s="6"/>
       <c r="AI31" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AJ31" s="13"/>
     </row>
     <row r="32" spans="1:36" ht="14.00" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I32" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>24</v>
@@ -4768,34 +4777,34 @@
       </c>
       <c r="AH32" s="6"/>
       <c r="AI32" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AJ32" s="13"/>
     </row>
     <row r="33" spans="1:36" ht="13.00" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I33" s="16" t="s">
         <v>13</v>
@@ -4807,7 +4816,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>13</v>
@@ -4848,8 +4857,8 @@
       <c r="Y33" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="Z33" s="17" t="s">
-        <v>24</v>
+      <c r="Z33" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="AA33" s="16" t="s">
         <v>24</v>
@@ -4874,16 +4883,16 @@
       </c>
       <c r="AH33" s="6"/>
       <c r="AI33" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AJ33" s="13"/>
     </row>
     <row r="34" spans="1:36" ht="14.00" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>13</v>
@@ -4980,7 +4989,7 @@
       </c>
       <c r="AH34" s="6"/>
       <c r="AI34" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ34" s="18">
         <v>4</v>
@@ -4988,10 +4997,10 @@
     </row>
     <row r="35" spans="1:36" ht="13.00" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>15</v>
@@ -5092,7 +5101,7 @@
     </row>
     <row r="36" spans="1:36" ht="14.00" customHeight="1">
       <c r="A36" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -5118,7 +5127,7 @@
       <c r="W36" s="25"/>
       <c r="X36" s="25"/>
       <c r="Y36" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z36" s="26"/>
       <c r="AA36" s="26"/>
@@ -5134,7 +5143,7 @@
     </row>
     <row r="37" spans="1:36" ht="22.00" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -5174,7 +5183,7 @@
     </row>
     <row r="38" spans="1:36" ht="46.50" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -231,7 +231,7 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
-      <t xml:space="preserve">学习</t>
+      <t xml:space="preserve">机</t>
     </r>
   </si>
   <si>
@@ -286,15 +286,6 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
-      <t xml:space="preserve">机</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
       <t xml:space="preserve">吴丽丽</t>
     </r>
   </si>
@@ -430,205 +421,205 @@
         <sz val="4.5"/>
         <rFont val="宋体"/>
       </rPr>
+      <t xml:space="preserve">宁雨露</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">黄琳</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">学习假</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">邓素君</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">杜倩</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">巴争</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">种萌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">蒋婷婷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">王文熙</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">赵伟</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">刘宇</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">郭紫烨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">余雷</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">邹姗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">郑思豪</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">黄红月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">邓江涛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">田静怡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">曾冠杰</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">曾燕霖</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">事假</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">林珊珊</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="宋体"/>
+      </rPr>
       <t xml:space="preserve">事假/值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">宁雨露</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">黄琳</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">学习假</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">邓素君</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">杜倩</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">巴争</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">种萌</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">蒋婷婷</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">王文熙</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">赵伟</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">刘宇</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">郭紫烨</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">余雷</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">邹姗</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">郑思豪</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">黄红月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">邓江涛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">田静怡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">曾冠杰</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">曾燕霖</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">事假</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="宋体"/>
-      </rPr>
-      <t xml:space="preserve">林珊珊</t>
     </r>
   </si>
   <si>
@@ -1875,14 +1866,14 @@
       <c r="AC5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AD5" s="20" t="s">
+      <c r="AD5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AE5" s="20" t="s">
-        <v>21</v>
+      <c r="AE5" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AG5" s="17" t="s">
         <v>13</v>
@@ -1892,7 +1883,7 @@
         <v>16</v>
       </c>
       <c r="AJ5" s="18">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="13.00" customHeight="1">
@@ -1983,24 +1974,24 @@
       <c r="AC6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE6" s="20" t="s">
-        <v>19</v>
+      <c r="AD6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="AG6" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="AH6" s="6"/>
       <c r="AI6" s="16" t="s">
         <v>23</v>
       </c>
       <c r="AJ6" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="14.00" customHeight="1">
@@ -2008,7 +1999,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>13</v>
@@ -2050,7 +2041,7 @@
         <v>13</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q7" s="16" t="s">
         <v>14</v>
@@ -2065,7 +2056,7 @@
         <v>24</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="V7" s="16" t="s">
         <v>19</v>
@@ -2094,8 +2085,8 @@
       <c r="AD7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AE7" s="20" t="s">
-        <v>14</v>
+      <c r="AE7" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="AF7" s="21" t="s">
         <v>26</v>
@@ -2105,18 +2096,18 @@
       </c>
       <c r="AH7" s="6"/>
       <c r="AI7" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ7" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="13.00" customHeight="1">
       <c r="A8" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>30</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>24</v>
@@ -2140,7 +2131,7 @@
         <v>14</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>25</v>
@@ -2191,7 +2182,7 @@
         <v>26</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="16" t="s">
         <v>19</v>
@@ -2205,26 +2196,26 @@
       <c r="AE8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AF8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG8" s="21" t="s">
-        <v>26</v>
+      <c r="AF8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG8" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AH8" s="6"/>
       <c r="AI8" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ8" s="22">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="14.00" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>20</v>
@@ -2257,7 +2248,7 @@
         <v>24</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N9" s="16" t="s">
         <v>25</v>
@@ -2321,28 +2312,28 @@
       </c>
       <c r="AH9" s="6"/>
       <c r="AI9" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AJ9" s="13"/>
     </row>
     <row r="10" spans="1:36" ht="13.00" customHeight="1">
       <c r="A10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>34</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>35</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>13</v>
@@ -2427,61 +2418,61 @@
       </c>
       <c r="AH10" s="6"/>
       <c r="AI10" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ10" s="13"/>
     </row>
     <row r="11" spans="1:36" ht="14.00" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="I11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="J11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="K11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="L11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>38</v>
-      </c>
       <c r="P11" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R11" s="17" t="s">
         <v>13</v>
@@ -2533,76 +2524,76 @@
       </c>
       <c r="AH11" s="6"/>
       <c r="AI11" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AJ11" s="13"/>
     </row>
     <row r="12" spans="1:36" ht="13.00" customHeight="1">
       <c r="A12" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="T12" s="16" t="s">
-        <v>40</v>
-      </c>
       <c r="U12" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V12" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W12" s="16" t="s">
         <v>24</v>
@@ -2639,35 +2630,35 @@
       </c>
       <c r="AH12" s="6"/>
       <c r="AI12" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AJ12" s="13"/>
     </row>
     <row r="13" spans="1:36" ht="13.00" customHeight="1">
       <c r="A13" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="I13" s="16" t="s">
         <v>24</v>
       </c>
@@ -2719,8 +2710,8 @@
       <c r="Y13" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Z13" s="20" t="s">
-        <v>43</v>
+      <c r="Z13" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="AA13" s="16" t="s">
         <v>24</v>
@@ -2745,34 +2736,34 @@
       </c>
       <c r="AH13" s="6"/>
       <c r="AI13" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AJ13" s="13"/>
     </row>
     <row r="14" spans="1:36" ht="14.00" customHeight="1">
       <c r="A14" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>24</v>
@@ -2783,8 +2774,8 @@
       <c r="K14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="20" t="s">
-        <v>34</v>
+      <c r="L14" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>13</v>
@@ -2792,8 +2783,8 @@
       <c r="N14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="20" t="s">
-        <v>35</v>
+      <c r="O14" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="P14" s="16" t="s">
         <v>25</v>
@@ -2851,7 +2842,7 @@
       </c>
       <c r="AH14" s="6"/>
       <c r="AI14" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ14" s="13"/>
     </row>
@@ -2860,7 +2851,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>13</v>
@@ -2878,7 +2869,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" s="16" t="s">
         <v>14</v>
@@ -2887,10 +2878,10 @@
         <v>18</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M15" s="19" t="s">
         <v>18</v>
@@ -2940,24 +2931,24 @@
       <c r="AB15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AC15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD15" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE15" s="20" t="s">
+      <c r="AC15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD15" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE15" s="16" t="s">
         <v>13</v>
       </c>
       <c r="AF15" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AG15" s="21" t="s">
-        <v>26</v>
+      <c r="AG15" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AH15" s="6"/>
       <c r="AI15" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AJ15" s="18">
         <v>-2</v>
@@ -2968,7 +2959,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>24</v>
@@ -3046,16 +3037,16 @@
         <v>14</v>
       </c>
       <c r="AB16" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC16" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE16" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AC16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE16" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="AF16" s="17" t="s">
         <v>13</v>
@@ -3065,10 +3056,10 @@
       </c>
       <c r="AH16" s="6"/>
       <c r="AI16" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AJ16" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="13.00" customHeight="1">
@@ -3076,7 +3067,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>20</v>
@@ -3163,7 +3154,7 @@
         <v>14</v>
       </c>
       <c r="AE17" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AF17" s="17" t="s">
         <v>19</v>
@@ -3173,7 +3164,7 @@
       </c>
       <c r="AH17" s="6"/>
       <c r="AI17" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ17" s="22">
         <v>3.5</v>
@@ -3181,10 +3172,10 @@
     </row>
     <row r="18" spans="1:36" ht="14.00" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>25</v>
@@ -3202,7 +3193,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>25</v>
@@ -3213,14 +3204,14 @@
       <c r="K18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L18" s="20" t="s">
-        <v>24</v>
+      <c r="L18" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>25</v>
@@ -3238,7 +3229,7 @@
         <v>14</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="U18" s="16" t="s">
         <v>25</v>
@@ -3267,8 +3258,8 @@
       <c r="AC18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD18" s="20" t="s">
-        <v>14</v>
+      <c r="AD18" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="AE18" s="16" t="s">
         <v>14</v>
@@ -3281,18 +3272,18 @@
       </c>
       <c r="AH18" s="6"/>
       <c r="AI18" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AJ18" s="18">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="13.00" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>24</v>
@@ -3316,10 +3307,10 @@
         <v>13</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L19" s="17" t="s">
         <v>25</v>
@@ -3337,7 +3328,7 @@
         <v>24</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="R19" s="17" t="s">
         <v>25</v>
@@ -3352,7 +3343,7 @@
         <v>14</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="W19" s="16" t="s">
         <v>24</v>
@@ -3375,69 +3366,71 @@
       <c r="AC19" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD19" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE19" s="20" t="s">
-        <v>21</v>
+      <c r="AD19" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE19" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="AF19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AG19" s="17" t="s">
-        <v>13</v>
+      <c r="AG19" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="AH19" s="6"/>
       <c r="AI19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ19" s="13"/>
+        <v>48</v>
+      </c>
+      <c r="AJ19" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:36" ht="14.00" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="I20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="J20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="K20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="L20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>38</v>
-      </c>
       <c r="N20" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P20" s="16" t="s">
         <v>13</v>
@@ -3495,40 +3488,40 @@
       </c>
       <c r="AH20" s="6"/>
       <c r="AI20" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AJ20" s="13"/>
     </row>
     <row r="21" spans="1:36" ht="13.00" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>25</v>
@@ -3537,7 +3530,7 @@
         <v>20</v>
       </c>
       <c r="M21" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N21" s="16" t="s">
         <v>13</v>
@@ -3601,34 +3594,34 @@
       </c>
       <c r="AH21" s="6"/>
       <c r="AI21" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AJ21" s="13"/>
     </row>
     <row r="22" spans="1:36" ht="13.00" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>24</v>
@@ -3707,34 +3700,34 @@
       </c>
       <c r="AH22" s="6"/>
       <c r="AI22" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AJ22" s="13"/>
     </row>
     <row r="23" spans="1:36" ht="14.00" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>25</v>
@@ -3813,49 +3806,49 @@
       </c>
       <c r="AH23" s="6"/>
       <c r="AI23" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AJ23" s="13"/>
     </row>
     <row r="24" spans="1:36" ht="13.00" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="N24" s="16" t="s">
         <v>24</v>
@@ -3919,7 +3912,7 @@
       </c>
       <c r="AH24" s="6"/>
       <c r="AI24" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AJ24" s="13"/>
     </row>
@@ -3928,7 +3921,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>13</v>
@@ -3991,7 +3984,7 @@
         <v>14</v>
       </c>
       <c r="W25" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="X25" s="16" t="s">
         <v>19</v>
@@ -4011,24 +4004,24 @@
       <c r="AC25" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AD25" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE25" s="20" t="s">
-        <v>25</v>
+      <c r="AD25" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE25" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="AF25" s="17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AG25" s="17" t="s">
         <v>13</v>
       </c>
       <c r="AH25" s="6"/>
       <c r="AI25" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AJ25" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:36" ht="13.00" customHeight="1">
@@ -4036,7 +4029,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>24</v>
@@ -4048,7 +4041,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>13</v>
@@ -4065,8 +4058,8 @@
       <c r="K26" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L26" s="20" t="s">
-        <v>24</v>
+      <c r="L26" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>14</v>
@@ -4117,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="AC26" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AD26" s="16" t="s">
         <v>19</v>
@@ -4133,10 +4126,10 @@
       </c>
       <c r="AH26" s="6"/>
       <c r="AI26" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AJ26" s="18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:36" ht="14.00" customHeight="1">
@@ -4144,7 +4137,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>19</v>
@@ -4227,8 +4220,8 @@
       <c r="AC27" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD27" s="20" t="s">
-        <v>18</v>
+      <c r="AD27" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="AE27" s="16" t="s">
         <v>14</v>
@@ -4241,7 +4234,7 @@
       </c>
       <c r="AH27" s="6"/>
       <c r="AI27" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AJ27" s="22">
         <v>1.5</v>
@@ -4249,10 +4242,10 @@
     </row>
     <row r="28" spans="1:36" ht="13.00" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>24</v>
@@ -4273,7 +4266,7 @@
         <v>24</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J28" s="16" t="s">
         <v>25</v>
@@ -4291,7 +4284,7 @@
         <v>14</v>
       </c>
       <c r="O28" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="P28" s="16" t="s">
         <v>25</v>
@@ -4335,8 +4328,8 @@
       <c r="AC28" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AD28" s="20" t="s">
-        <v>14</v>
+      <c r="AD28" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="AE28" s="16" t="s">
         <v>13</v>
@@ -4349,10 +4342,10 @@
       </c>
       <c r="AH28" s="6"/>
       <c r="AI28" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AJ28" s="22">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29" spans="1:36" ht="14.00" customHeight="1">
@@ -4360,7 +4353,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>13</v>
@@ -4372,7 +4365,7 @@
         <v>13</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>25</v>
@@ -4426,7 +4419,7 @@
         <v>14</v>
       </c>
       <c r="X29" s="16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y29" s="17" t="s">
         <v>25</v>
@@ -4443,50 +4436,48 @@
       <c r="AC29" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AD29" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE29" s="20" t="s">
-        <v>21</v>
+      <c r="AD29" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="AF29" s="17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AG29" s="17" t="s">
         <v>13</v>
       </c>
       <c r="AH29" s="6"/>
       <c r="AI29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ29" s="18">
-        <v>-1</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AJ29" s="13"/>
     </row>
     <row r="30" spans="1:36" ht="13.00" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>24</v>
@@ -4565,34 +4556,34 @@
       </c>
       <c r="AH30" s="6"/>
       <c r="AI30" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AJ30" s="13"/>
     </row>
     <row r="31" spans="1:36" ht="13.00" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>25</v>
@@ -4671,40 +4662,40 @@
       </c>
       <c r="AH31" s="6"/>
       <c r="AI31" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AJ31" s="13"/>
     </row>
     <row r="32" spans="1:36" ht="14.00" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I32" s="16" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>24</v>
@@ -4777,34 +4768,34 @@
       </c>
       <c r="AH32" s="6"/>
       <c r="AI32" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AJ32" s="13"/>
     </row>
     <row r="33" spans="1:36" ht="13.00" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I33" s="16" t="s">
         <v>13</v>
@@ -4816,7 +4807,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>13</v>
@@ -4857,8 +4848,8 @@
       <c r="Y33" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="Z33" s="20" t="s">
-        <v>43</v>
+      <c r="Z33" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="AA33" s="16" t="s">
         <v>24</v>
@@ -4883,16 +4874,16 @@
       </c>
       <c r="AH33" s="6"/>
       <c r="AI33" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AJ33" s="13"/>
     </row>
     <row r="34" spans="1:36" ht="14.00" customHeight="1">
       <c r="A34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>13</v>
@@ -4989,7 +4980,7 @@
       </c>
       <c r="AH34" s="6"/>
       <c r="AI34" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AJ34" s="18">
         <v>4</v>
@@ -4997,10 +4988,10 @@
     </row>
     <row r="35" spans="1:36" ht="13.00" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>15</v>
@@ -5101,7 +5092,7 @@
     </row>
     <row r="36" spans="1:36" ht="14.00" customHeight="1">
       <c r="A36" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -5127,7 +5118,7 @@
       <c r="W36" s="25"/>
       <c r="X36" s="25"/>
       <c r="Y36" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z36" s="26"/>
       <c r="AA36" s="26"/>
@@ -5143,7 +5134,7 @@
     </row>
     <row r="37" spans="1:36" ht="22.00" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -5183,7 +5174,7 @@
     </row>
     <row r="38" spans="1:36" ht="46.50" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
